--- a/Template_Horarios_Grupos_Vespertino.xlsx
+++ b/Template_Horarios_Grupos_Vespertino.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Customers\CBTis73\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{486E29B6-E3B7-4880-8B50-80F8C32709BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62208206-3A4B-4D1F-B2C3-3668DE8522D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="36">
   <si>
     <t>Centro de Bachillerato Tecnologico</t>
   </si>
@@ -108,24 +108,6 @@
     <t>19:15 - 20:00</t>
   </si>
   <si>
-    <t>INGLÉS I</t>
-  </si>
-  <si>
-    <t>LENG. Y COM. I</t>
-  </si>
-  <si>
-    <t>PENS. MAT. I</t>
-  </si>
-  <si>
-    <t>CULT. DIGITAL I</t>
-  </si>
-  <si>
-    <t>CIENCIAS SOCIALES I</t>
-  </si>
-  <si>
-    <t>TUTORÍAS</t>
-  </si>
-  <si>
     <t>YOLANDA MORALES MIRANDA</t>
   </si>
   <si>
@@ -144,12 +126,6 @@
     <t>DIRECTOR</t>
   </si>
   <si>
-    <t>CIENCIAS NAT. I</t>
-  </si>
-  <si>
-    <t>PENS. FIL. Y HUM. I</t>
-  </si>
-  <si>
     <t>Semestre: Agosto 2026 - Enero 2027</t>
   </si>
   <si>
@@ -160,9 +136,6 @@
   </si>
   <si>
     <t>Cd. Rio Bravo Tamaulipas a  de agosto de 2026</t>
-  </si>
-  <si>
-    <t>SALUD EMS</t>
   </si>
 </sst>
 </file>
@@ -504,26 +477,17 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -531,14 +495,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="20" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1484,7 +1457,7 @@
       <c r="D5" s="56"/>
       <c r="E5" s="56"/>
       <c r="F5" s="57" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="6"/>
@@ -1522,7 +1495,7 @@
       </c>
       <c r="D7" s="59"/>
       <c r="E7" s="60" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F7" s="60"/>
       <c r="G7" s="60"/>
@@ -2010,16 +1983,14 @@
     </row>
     <row r="29" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="19"/>
-      <c r="B29" s="14" t="s">
-        <v>28</v>
-      </c>
+      <c r="B29" s="14"/>
       <c r="C29" s="12">
         <v>4</v>
       </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="37"/>
       <c r="H29" s="9"/>
       <c r="I29" s="5"/>
       <c r="J29">
@@ -2035,16 +2006,14 @@
     </row>
     <row r="30" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="19"/>
-      <c r="B30" s="14" t="s">
-        <v>26</v>
-      </c>
+      <c r="B30" s="14"/>
       <c r="C30" s="12">
         <v>3</v>
       </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="39"/>
       <c r="H30" s="9"/>
       <c r="I30" s="5"/>
       <c r="J30">
@@ -2060,16 +2029,14 @@
     </row>
     <row r="31" spans="1:15" s="10" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="19"/>
-      <c r="B31" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B31" s="15"/>
       <c r="C31" s="12">
         <v>4</v>
       </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="41"/>
       <c r="H31" s="9"/>
       <c r="I31" s="5"/>
       <c r="J31">
@@ -2085,16 +2052,14 @@
     </row>
     <row r="32" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="18"/>
-      <c r="B32" s="16" t="s">
-        <v>29</v>
-      </c>
+      <c r="B32" s="16"/>
       <c r="C32" s="17">
         <v>3</v>
       </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="43"/>
       <c r="H32" s="9"/>
       <c r="I32" s="5"/>
       <c r="J32">
@@ -2106,16 +2071,14 @@
     </row>
     <row r="33" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="18"/>
-      <c r="B33" s="14" t="s">
-        <v>39</v>
-      </c>
+      <c r="B33" s="14"/>
       <c r="C33" s="12">
         <v>4</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="38"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="37"/>
       <c r="H33" s="9"/>
       <c r="I33" s="5"/>
       <c r="J33">
@@ -2127,16 +2090,14 @@
     </row>
     <row r="34" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="18"/>
-      <c r="B34" s="14" t="s">
-        <v>27</v>
-      </c>
+      <c r="B34" s="14"/>
       <c r="C34" s="12">
         <v>3</v>
       </c>
-      <c r="D34" s="36"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="38"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="37"/>
       <c r="H34" s="9"/>
       <c r="I34" s="5"/>
       <c r="J34">
@@ -2148,16 +2109,14 @@
     </row>
     <row r="35" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="18"/>
-      <c r="B35" s="14" t="s">
-        <v>30</v>
-      </c>
+      <c r="B35" s="14"/>
       <c r="C35" s="12">
         <v>2</v>
       </c>
-      <c r="D35" s="39"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="41"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="39"/>
       <c r="H35" s="9"/>
       <c r="I35" s="5"/>
       <c r="J35">
@@ -2169,16 +2128,14 @@
     </row>
     <row r="36" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="18"/>
-      <c r="B36" s="14" t="s">
-        <v>31</v>
-      </c>
+      <c r="B36" s="14"/>
       <c r="C36" s="12">
         <v>1</v>
       </c>
-      <c r="D36" s="36"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="38"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="37"/>
       <c r="H36" s="9"/>
       <c r="I36" s="5"/>
       <c r="J36">
@@ -2190,16 +2147,14 @@
     </row>
     <row r="37" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="18"/>
-      <c r="B37" s="14" t="s">
-        <v>44</v>
-      </c>
+      <c r="B37" s="14"/>
       <c r="C37" s="12">
         <v>2</v>
       </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="41"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="39"/>
       <c r="H37" s="9"/>
       <c r="I37" s="5"/>
     </row>
@@ -2297,12 +2252,12 @@
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="18"/>
       <c r="B44" s="75" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C44" s="75"/>
       <c r="D44" s="75"/>
       <c r="E44" s="75" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F44" s="75"/>
       <c r="G44" s="75"/>
@@ -2317,12 +2272,12 @@
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="18"/>
       <c r="B45" s="76" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C45" s="76"/>
       <c r="D45" s="76"/>
       <c r="E45" s="76" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F45" s="76"/>
       <c r="G45" s="76"/>
@@ -2369,12 +2324,12 @@
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="18"/>
       <c r="B48" s="75" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C48" s="75"/>
       <c r="D48" s="75"/>
       <c r="E48" s="75" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F48" s="75"/>
       <c r="G48" s="75"/>
@@ -2395,7 +2350,7 @@
       <c r="C49" s="76"/>
       <c r="D49" s="76"/>
       <c r="E49" s="76" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F49" s="76"/>
       <c r="G49" s="76"/>
@@ -2413,7 +2368,7 @@
       <c r="B50" s="29"/>
       <c r="C50" s="29"/>
       <c r="D50" s="77" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E50" s="77"/>
       <c r="F50" s="77"/>

--- a/Template_Horarios_Grupos_Vespertino.xlsx
+++ b/Template_Horarios_Grupos_Vespertino.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Customers\CBTis73\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62208206-3A4B-4D1F-B2C3-3668DE8522D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB999ECF-13AF-4BA7-BECA-79216299B7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="GRUPO" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">GRUPO!$A$1:$H$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">GRUPO!$A$1:$H$56</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="36">
   <si>
     <t>Centro de Bachillerato Tecnologico</t>
   </si>
@@ -390,7 +390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -513,22 +513,82 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="20" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="20" fontId="23" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="23" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -551,57 +611,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="21" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -679,13 +688,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>148167</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -729,13 +738,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>227541</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>185208</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>854870</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>188119</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -779,13 +788,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>154782</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>773906</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>166688</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -829,13 +838,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>92870</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>854869</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>164306</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -879,13 +888,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>148167</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -929,13 +938,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>227541</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>185208</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>854870</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>188119</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -979,13 +988,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>148167</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1029,13 +1038,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>227541</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>185208</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>854870</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>188119</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1379,7 +1388,7 @@
     <tabColor rgb="FF00B0F0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="15.73046875" customWidth="1"/>
@@ -1406,12 +1415,12 @@
       <c r="A2" s="18"/>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
       <c r="H2" s="1"/>
       <c r="I2" s="2"/>
     </row>
@@ -1419,12 +1428,12 @@
       <c r="A3" s="18"/>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
       <c r="H3" s="4"/>
       <c r="I3" s="5"/>
       <c r="J3">
@@ -1454,12 +1463,12 @@
       <c r="A5" s="18"/>
       <c r="B5" s="20"/>
       <c r="C5" s="21"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="57" t="s">
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="57"/>
+      <c r="G5" s="77"/>
       <c r="H5" s="6"/>
       <c r="I5" s="5"/>
       <c r="J5">
@@ -1490,15 +1499,15 @@
       <c r="B7" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="59"/>
-      <c r="E7" s="60" t="s">
+      <c r="D7" s="79"/>
+      <c r="E7" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
       <c r="H7" s="7"/>
       <c r="I7" s="5"/>
       <c r="J7">
@@ -1558,14 +1567,14 @@
     </row>
     <row r="10" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="19"/>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
       <c r="H10" s="9"/>
       <c r="I10" s="5"/>
       <c r="J10">
@@ -1581,12 +1590,12 @@
     </row>
     <row r="11" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="19"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
       <c r="H11" s="9"/>
       <c r="I11" s="5"/>
       <c r="J11">
@@ -1602,14 +1611,14 @@
     </row>
     <row r="12" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="19"/>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="48"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
       <c r="H12" s="9"/>
       <c r="I12" s="5"/>
       <c r="J12">
@@ -1625,12 +1634,12 @@
     </row>
     <row r="13" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="19"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
       <c r="H13" s="9"/>
       <c r="I13" s="5"/>
       <c r="J13">
@@ -1646,14 +1655,14 @@
     </row>
     <row r="14" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="19"/>
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="64"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="66"/>
       <c r="H14" s="9"/>
       <c r="I14" s="5"/>
       <c r="J14">
@@ -1669,12 +1678,12 @@
     </row>
     <row r="15" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="19"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="65"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="67"/>
       <c r="H15" s="9"/>
       <c r="I15" s="5"/>
       <c r="J15">
@@ -1693,13 +1702,13 @@
       <c r="B16" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="68"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="70"/>
       <c r="H16" s="9"/>
       <c r="I16" s="5"/>
       <c r="J16">
@@ -1715,14 +1724,14 @@
     </row>
     <row r="17" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="19"/>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
       <c r="H17" s="9"/>
       <c r="I17" s="5"/>
       <c r="J17">
@@ -1738,12 +1747,12 @@
     </row>
     <row r="18" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="19"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
       <c r="H18" s="9"/>
       <c r="I18" s="5"/>
       <c r="J18">
@@ -1759,14 +1768,14 @@
     </row>
     <row r="19" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="19"/>
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="62"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
       <c r="H19" s="9"/>
       <c r="I19" s="5"/>
       <c r="J19">
@@ -1782,12 +1791,12 @@
     </row>
     <row r="20" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="19"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
       <c r="H20" s="9"/>
       <c r="I20" s="5"/>
       <c r="J20">
@@ -1803,14 +1812,14 @@
     </row>
     <row r="21" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="19"/>
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
       <c r="H21" s="9"/>
       <c r="I21" s="5"/>
       <c r="J21">
@@ -1826,12 +1835,12 @@
     </row>
     <row r="22" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="19"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
       <c r="H22" s="9"/>
       <c r="I22" s="5"/>
       <c r="J22">
@@ -1847,14 +1856,14 @@
     </row>
     <row r="23" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="19"/>
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
       <c r="H23" s="9"/>
       <c r="I23" s="5"/>
       <c r="J23">
@@ -1870,12 +1879,12 @@
     </row>
     <row r="24" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="19"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
       <c r="H24" s="9"/>
       <c r="I24" s="5"/>
       <c r="J24">
@@ -1891,14 +1900,14 @@
     </row>
     <row r="25" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="19"/>
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
       <c r="H25" s="9"/>
       <c r="I25" s="5"/>
       <c r="J25">
@@ -1914,12 +1923,12 @@
     </row>
     <row r="26" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="19"/>
-      <c r="B26" s="61"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
       <c r="H26" s="9"/>
       <c r="I26" s="5"/>
       <c r="J26">
@@ -2174,13 +2183,13 @@
       <c r="B39" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="69" t="s">
+      <c r="C39" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="71"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="61"/>
       <c r="H39" s="9"/>
       <c r="I39" s="5"/>
       <c r="J39">
@@ -2193,11 +2202,11 @@
     <row r="40" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="18"/>
       <c r="B40" s="27"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="73"/>
-      <c r="E40" s="73"/>
-      <c r="F40" s="73"/>
-      <c r="G40" s="74"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="56"/>
       <c r="H40" s="9"/>
       <c r="I40" s="5"/>
       <c r="J40">
@@ -2210,133 +2219,94 @@
     <row r="41" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="18"/>
       <c r="B41" s="27"/>
-      <c r="C41" s="72"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="73"/>
-      <c r="F41" s="73"/>
-      <c r="G41" s="74"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="9"/>
       <c r="I41" s="5"/>
-      <c r="J41">
-        <v>39</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="42" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="18"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="9"/>
       <c r="I42" s="5"/>
     </row>
-    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="18"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="9"/>
       <c r="I43" s="5"/>
-      <c r="J43">
-        <v>40</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="44" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="18"/>
-      <c r="B44" s="75" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" s="75"/>
-      <c r="D44" s="75"/>
-      <c r="E44" s="75" t="s">
-        <v>26</v>
-      </c>
-      <c r="F44" s="75"/>
-      <c r="G44" s="75"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="50"/>
+      <c r="H44" s="9"/>
       <c r="I44" s="5"/>
-      <c r="J44">
-        <v>41</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="45" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="18"/>
-      <c r="B45" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="C45" s="76"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="F45" s="76"/>
-      <c r="G45" s="76"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="50"/>
       <c r="I45" s="5"/>
       <c r="J45">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="18"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="49"/>
+      <c r="F46" s="49"/>
+      <c r="G46" s="50"/>
       <c r="I46" s="5"/>
-      <c r="J46">
-        <v>43</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="47" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="18"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="50"/>
       <c r="I47" s="5"/>
-      <c r="J47">
-        <v>44</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="48" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="18"/>
-      <c r="B48" s="75" t="s">
-        <v>29</v>
-      </c>
-      <c r="C48" s="75"/>
-      <c r="D48" s="75"/>
-      <c r="E48" s="75" t="s">
-        <v>34</v>
-      </c>
-      <c r="F48" s="75"/>
-      <c r="G48" s="75"/>
-      <c r="H48" s="8"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="50"/>
       <c r="I48" s="5"/>
       <c r="J48">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>2</v>
@@ -2344,20 +2314,15 @@
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="18"/>
-      <c r="B49" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="C49" s="76"/>
-      <c r="D49" s="76"/>
-      <c r="E49" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="F49" s="76"/>
-      <c r="G49" s="76"/>
-      <c r="H49" s="8"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
       <c r="I49" s="5"/>
       <c r="J49">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>2</v>
@@ -2365,107 +2330,226 @@
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="18"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="77" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="77"/>
-      <c r="F50" s="77"/>
-      <c r="G50" s="77"/>
-      <c r="H50" s="8"/>
+      <c r="B50" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="51"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51"/>
       <c r="I50" s="5"/>
       <c r="J50">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B51" s="20"/>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="8"/>
+      <c r="A51" s="18"/>
+      <c r="B51" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="52"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
       <c r="I51" s="5"/>
       <c r="J51">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B52" s="20"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="8"/>
+      <c r="A52" s="18"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
       <c r="I52" s="5"/>
       <c r="J52">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="18"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
       <c r="I53" s="5"/>
       <c r="J53">
+        <v>44</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="18"/>
+      <c r="B54" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54" s="51"/>
+      <c r="D54" s="51"/>
+      <c r="E54" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="F54" s="51"/>
+      <c r="G54" s="51"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="5"/>
+      <c r="J54">
+        <v>45</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="18"/>
+      <c r="B55" s="52" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="52"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F55" s="52"/>
+      <c r="G55" s="52"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="5"/>
+      <c r="J55">
+        <v>46</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="18"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="53"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="5"/>
+      <c r="J56">
+        <v>47</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B57" s="20"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="5"/>
+      <c r="J57">
+        <v>48</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="5"/>
+      <c r="J58">
+        <v>49</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I59" s="5"/>
+      <c r="J59">
         <v>50</v>
       </c>
-      <c r="L53" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="L57" s="13"/>
-    </row>
-    <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="L58" s="13"/>
-    </row>
-    <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="L59" s="13"/>
-    </row>
-    <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="L60" s="13"/>
-    </row>
-    <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="L61" s="13"/>
+      <c r="L59" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L63" s="13"/>
+    </row>
+    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L64" s="13"/>
+    </row>
+    <row r="65" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L65" s="13"/>
+    </row>
+    <row r="66" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L66" s="13"/>
+    </row>
+    <row r="67" spans="12:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L67" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
+  <mergeCells count="66">
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="G23:G24"/>
     <mergeCell ref="G25:G26"/>
@@ -2482,34 +2566,28 @@
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="D56:G56"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup scale="92" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/Template_Horarios_Grupos_Vespertino.xlsx
+++ b/Template_Horarios_Grupos_Vespertino.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Customers\CBTis73\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB999ECF-13AF-4BA7-BECA-79216299B7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FA657E-C99A-49B2-9E89-59B7F19E83ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -513,13 +513,76 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="23" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="23" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="21" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -532,85 +595,22 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="21" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="23" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="23" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1415,12 +1415,12 @@
       <c r="A2" s="18"/>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
-      <c r="D2" s="74" t="s">
+      <c r="D2" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
       <c r="H2" s="1"/>
       <c r="I2" s="2"/>
     </row>
@@ -1428,12 +1428,12 @@
       <c r="A3" s="18"/>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
       <c r="H3" s="4"/>
       <c r="I3" s="5"/>
       <c r="J3">
@@ -1463,12 +1463,12 @@
       <c r="A5" s="18"/>
       <c r="B5" s="20"/>
       <c r="C5" s="21"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="77" t="s">
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="77"/>
+      <c r="G5" s="57"/>
       <c r="H5" s="6"/>
       <c r="I5" s="5"/>
       <c r="J5">
@@ -1499,15 +1499,15 @@
       <c r="B7" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="78" t="s">
+      <c r="C7" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="79"/>
-      <c r="E7" s="80" t="s">
+      <c r="D7" s="59"/>
+      <c r="E7" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
       <c r="H7" s="7"/>
       <c r="I7" s="5"/>
       <c r="J7">
@@ -1567,14 +1567,14 @@
     </row>
     <row r="10" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="19"/>
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
       <c r="H10" s="9"/>
       <c r="I10" s="5"/>
       <c r="J10">
@@ -1590,12 +1590,12 @@
     </row>
     <row r="11" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="19"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
       <c r="H11" s="9"/>
       <c r="I11" s="5"/>
       <c r="J11">
@@ -1611,14 +1611,14 @@
     </row>
     <row r="12" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="19"/>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
       <c r="H12" s="9"/>
       <c r="I12" s="5"/>
       <c r="J12">
@@ -1634,12 +1634,12 @@
     </row>
     <row r="13" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="19"/>
-      <c r="B13" s="63"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
       <c r="H13" s="9"/>
       <c r="I13" s="5"/>
       <c r="J13">
@@ -1655,14 +1655,14 @@
     </row>
     <row r="14" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="19"/>
-      <c r="B14" s="71" t="s">
+      <c r="B14" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="66"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="64"/>
       <c r="H14" s="9"/>
       <c r="I14" s="5"/>
       <c r="J14">
@@ -1678,12 +1678,12 @@
     </row>
     <row r="15" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="19"/>
-      <c r="B15" s="72"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="67"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="65"/>
       <c r="H15" s="9"/>
       <c r="I15" s="5"/>
       <c r="J15">
@@ -1702,13 +1702,13 @@
       <c r="B16" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="70"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="68"/>
       <c r="H16" s="9"/>
       <c r="I16" s="5"/>
       <c r="J16">
@@ -1724,14 +1724,14 @@
     </row>
     <row r="17" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="19"/>
-      <c r="B17" s="62" t="s">
+      <c r="B17" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="64"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
       <c r="H17" s="9"/>
       <c r="I17" s="5"/>
       <c r="J17">
@@ -1747,12 +1747,12 @@
     </row>
     <row r="18" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="19"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
       <c r="H18" s="9"/>
       <c r="I18" s="5"/>
       <c r="J18">
@@ -1768,14 +1768,14 @@
     </row>
     <row r="19" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="19"/>
-      <c r="B19" s="62" t="s">
+      <c r="B19" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="64"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
       <c r="H19" s="9"/>
       <c r="I19" s="5"/>
       <c r="J19">
@@ -1791,12 +1791,12 @@
     </row>
     <row r="20" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="19"/>
-      <c r="B20" s="63"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
       <c r="H20" s="9"/>
       <c r="I20" s="5"/>
       <c r="J20">
@@ -1812,14 +1812,14 @@
     </row>
     <row r="21" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="19"/>
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="57"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
       <c r="H21" s="9"/>
       <c r="I21" s="5"/>
       <c r="J21">
@@ -1835,12 +1835,12 @@
     </row>
     <row r="22" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="19"/>
-      <c r="B22" s="63"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
       <c r="H22" s="9"/>
       <c r="I22" s="5"/>
       <c r="J22">
@@ -1856,14 +1856,14 @@
     </row>
     <row r="23" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="19"/>
-      <c r="B23" s="62" t="s">
+      <c r="B23" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
       <c r="H23" s="9"/>
       <c r="I23" s="5"/>
       <c r="J23">
@@ -1879,12 +1879,12 @@
     </row>
     <row r="24" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="19"/>
-      <c r="B24" s="63"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
       <c r="H24" s="9"/>
       <c r="I24" s="5"/>
       <c r="J24">
@@ -1900,14 +1900,14 @@
     </row>
     <row r="25" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="19"/>
-      <c r="B25" s="73" t="s">
+      <c r="B25" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
       <c r="H25" s="9"/>
       <c r="I25" s="5"/>
       <c r="J25">
@@ -1923,12 +1923,12 @@
     </row>
     <row r="26" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="19"/>
-      <c r="B26" s="73"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
+      <c r="B26" s="61"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
       <c r="H26" s="9"/>
       <c r="I26" s="5"/>
       <c r="J26">
@@ -2183,13 +2183,13 @@
       <c r="B39" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="59" t="s">
+      <c r="C39" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="61"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="71"/>
       <c r="H39" s="9"/>
       <c r="I39" s="5"/>
       <c r="J39">
@@ -2202,11 +2202,11 @@
     <row r="40" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="18"/>
       <c r="B40" s="27"/>
-      <c r="C40" s="54"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="56"/>
+      <c r="C40" s="75"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="77"/>
       <c r="H40" s="9"/>
       <c r="I40" s="5"/>
       <c r="J40">
@@ -2219,55 +2219,55 @@
     <row r="41" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="18"/>
       <c r="B41" s="27"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="49"/>
-      <c r="F41" s="49"/>
-      <c r="G41" s="50"/>
+      <c r="C41" s="78"/>
+      <c r="D41" s="79"/>
+      <c r="E41" s="79"/>
+      <c r="F41" s="79"/>
+      <c r="G41" s="80"/>
       <c r="H41" s="9"/>
       <c r="I41" s="5"/>
     </row>
     <row r="42" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="18"/>
       <c r="B42" s="27"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="49"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="49"/>
-      <c r="G42" s="50"/>
+      <c r="C42" s="78"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="79"/>
+      <c r="F42" s="79"/>
+      <c r="G42" s="80"/>
       <c r="H42" s="9"/>
       <c r="I42" s="5"/>
     </row>
     <row r="43" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="18"/>
       <c r="B43" s="27"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="50"/>
+      <c r="C43" s="78"/>
+      <c r="D43" s="79"/>
+      <c r="E43" s="79"/>
+      <c r="F43" s="79"/>
+      <c r="G43" s="80"/>
       <c r="H43" s="9"/>
       <c r="I43" s="5"/>
     </row>
     <row r="44" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="18"/>
       <c r="B44" s="27"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="49"/>
-      <c r="E44" s="49"/>
-      <c r="F44" s="49"/>
-      <c r="G44" s="50"/>
+      <c r="C44" s="78"/>
+      <c r="D44" s="79"/>
+      <c r="E44" s="79"/>
+      <c r="F44" s="79"/>
+      <c r="G44" s="80"/>
       <c r="H44" s="9"/>
       <c r="I44" s="5"/>
     </row>
     <row r="45" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="18"/>
       <c r="B45" s="27"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="50"/>
+      <c r="C45" s="78"/>
+      <c r="D45" s="79"/>
+      <c r="E45" s="79"/>
+      <c r="F45" s="79"/>
+      <c r="G45" s="80"/>
       <c r="I45" s="5"/>
       <c r="J45">
         <v>39</v>
@@ -2279,31 +2279,31 @@
     <row r="46" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="18"/>
       <c r="B46" s="27"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="49"/>
-      <c r="E46" s="49"/>
-      <c r="F46" s="49"/>
-      <c r="G46" s="50"/>
+      <c r="C46" s="78"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="79"/>
+      <c r="F46" s="79"/>
+      <c r="G46" s="80"/>
       <c r="I46" s="5"/>
     </row>
     <row r="47" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="18"/>
       <c r="B47" s="27"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="50"/>
+      <c r="C47" s="78"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="79"/>
+      <c r="F47" s="79"/>
+      <c r="G47" s="80"/>
       <c r="I47" s="5"/>
     </row>
     <row r="48" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="18"/>
       <c r="B48" s="27"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="50"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="79"/>
+      <c r="E48" s="79"/>
+      <c r="F48" s="79"/>
+      <c r="G48" s="80"/>
       <c r="I48" s="5"/>
       <c r="J48">
         <v>39</v>
@@ -2330,16 +2330,16 @@
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="18"/>
-      <c r="B50" s="51" t="s">
+      <c r="B50" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51" t="s">
+      <c r="C50" s="72"/>
+      <c r="D50" s="72"/>
+      <c r="E50" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
+      <c r="F50" s="72"/>
+      <c r="G50" s="72"/>
       <c r="I50" s="5"/>
       <c r="J50">
         <v>41</v>
@@ -2350,16 +2350,16 @@
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="18"/>
-      <c r="B51" s="52" t="s">
+      <c r="B51" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="C51" s="52"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52" t="s">
+      <c r="C51" s="73"/>
+      <c r="D51" s="73"/>
+      <c r="E51" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="F51" s="52"/>
-      <c r="G51" s="52"/>
+      <c r="F51" s="73"/>
+      <c r="G51" s="73"/>
       <c r="I51" s="5"/>
       <c r="J51">
         <v>42</v>
@@ -2402,16 +2402,16 @@
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="18"/>
-      <c r="B54" s="51" t="s">
+      <c r="B54" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="C54" s="51"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="51" t="s">
+      <c r="C54" s="72"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="F54" s="51"/>
-      <c r="G54" s="51"/>
+      <c r="F54" s="72"/>
+      <c r="G54" s="72"/>
       <c r="H54" s="8"/>
       <c r="I54" s="5"/>
       <c r="J54">
@@ -2423,16 +2423,16 @@
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="18"/>
-      <c r="B55" s="52" t="s">
+      <c r="B55" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="C55" s="52"/>
-      <c r="D55" s="52"/>
-      <c r="E55" s="52" t="s">
+      <c r="C55" s="73"/>
+      <c r="D55" s="73"/>
+      <c r="E55" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="F55" s="52"/>
-      <c r="G55" s="52"/>
+      <c r="F55" s="73"/>
+      <c r="G55" s="73"/>
       <c r="H55" s="8"/>
       <c r="I55" s="5"/>
       <c r="J55">
@@ -2446,12 +2446,12 @@
       <c r="A56" s="18"/>
       <c r="B56" s="29"/>
       <c r="C56" s="29"/>
-      <c r="D56" s="53" t="s">
+      <c r="D56" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="E56" s="53"/>
-      <c r="F56" s="53"/>
-      <c r="G56" s="53"/>
+      <c r="E56" s="74"/>
+      <c r="F56" s="74"/>
+      <c r="G56" s="74"/>
       <c r="H56" s="8"/>
       <c r="I56" s="5"/>
       <c r="J56">
@@ -2522,34 +2522,28 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="D56:G56"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="G23:G24"/>
     <mergeCell ref="G25:G26"/>
@@ -2566,28 +2560,34 @@
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="D56:G56"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup scale="92" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
